--- a/shipmentstatusdata.xlsx
+++ b/shipmentstatusdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pearlglobal1-my.sharepoint.com/personal/rohan_kataria_pearlglobal_com/Documents/Desktop/Pearl Global Central/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{2DC4E581-1014-4DBC-8659-815F30CF3D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11ADFE69-E093-4EC0-8FD0-4792601B7609}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{2DC4E581-1014-4DBC-8659-815F30CF3D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0E5E61-DE6F-42B9-AFFA-098811875A89}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CAD55008-ED28-4F70-B62E-27BB82954684}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="269">
   <si>
     <t>SONo</t>
   </si>
@@ -824,6 +824,9 @@
   </si>
   <si>
     <t>26-09-26</t>
+  </si>
+  <si>
+    <t>Tough to Ship</t>
   </si>
 </sst>
 </file>
@@ -1354,10 +1357,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1680,6 +1679,7 @@
   <cols>
     <col min="3" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1927,7 +1927,7 @@
         <v>36</v>
       </c>
       <c r="N4" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O4">
         <v>36</v>
@@ -1995,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O5">
         <v>12</v>
@@ -2063,7 +2063,7 @@
         <v>60</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O6">
         <v>60</v>
@@ -2131,7 +2131,7 @@
         <v>48</v>
       </c>
       <c r="N7" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O7">
         <v>48</v>
@@ -3254,7 +3254,7 @@
         <v>624</v>
       </c>
       <c r="N24" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>171</v>
       </c>
       <c r="N28" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>1070</v>
       </c>
       <c r="N34" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>102</v>
       </c>
       <c r="N54" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -5245,7 +5245,7 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -5307,7 +5307,7 @@
         <v>34</v>
       </c>
       <c r="N56" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>34</v>
       </c>
       <c r="N57" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -5431,7 +5431,7 @@
         <v>2824</v>
       </c>
       <c r="N58" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -5496,7 +5496,7 @@
         <v>20</v>
       </c>
       <c r="N59" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -5564,7 +5564,7 @@
         <v>16</v>
       </c>
       <c r="N60" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O60">
         <v>16</v>
@@ -5632,7 +5632,7 @@
         <v>84</v>
       </c>
       <c r="N61" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O61">
         <v>84</v>
@@ -5694,7 +5694,7 @@
         <v>34</v>
       </c>
       <c r="N62" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         <v>34</v>
       </c>
       <c r="N63" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>110</v>
       </c>
       <c r="N64" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O64">
         <v>110</v>
@@ -5892,7 +5892,7 @@
         <v>7305</v>
       </c>
       <c r="N65" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -5960,7 +5960,7 @@
         <v>124</v>
       </c>
       <c r="N66" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -6028,7 +6028,7 @@
         <v>64</v>
       </c>
       <c r="N67" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O67">
         <v>64</v>
@@ -6096,7 +6096,7 @@
         <v>80</v>
       </c>
       <c r="N68" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O68">
         <v>80</v>
@@ -6164,7 +6164,7 @@
         <v>16</v>
       </c>
       <c r="N69" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O69">
         <v>16</v>
@@ -6229,7 +6229,7 @@
         <v>940</v>
       </c>
       <c r="N70" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O70">
         <v>940</v>
@@ -7328,7 +7328,7 @@
         <v>34</v>
       </c>
       <c r="N87" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -7390,7 +7390,7 @@
         <v>68</v>
       </c>
       <c r="N88" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>102</v>
       </c>
       <c r="N95" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -7886,7 +7886,7 @@
         <v>17</v>
       </c>
       <c r="N96" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -9059,7 +9059,7 @@
         <v>1516</v>
       </c>
       <c r="N114" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O114">
         <v>1516</v>
@@ -9124,7 +9124,7 @@
         <v>190</v>
       </c>
       <c r="N115" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -9186,7 +9186,7 @@
         <v>3277</v>
       </c>
       <c r="N116" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -9248,7 +9248,7 @@
         <v>6251</v>
       </c>
       <c r="N117" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -9310,7 +9310,7 @@
         <v>4800</v>
       </c>
       <c r="N118" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -10114,7 +10114,7 @@
         <v>47</v>
       </c>
       <c r="N130" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -10309,7 +10309,7 @@
         <v>288</v>
       </c>
       <c r="N133" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -10566,7 +10566,7 @@
         <v>180</v>
       </c>
       <c r="N137" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -11452,7 +11452,7 @@
         <v>60</v>
       </c>
       <c r="N151" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>1368</v>
       </c>
       <c r="N156" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -11836,7 +11836,7 @@
         <v>528</v>
       </c>
       <c r="N157" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O157">
         <v>0</v>
@@ -11901,7 +11901,7 @@
         <v>1800</v>
       </c>
       <c r="N158" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O158">
         <v>0</v>
@@ -12096,7 +12096,7 @@
         <v>2688</v>
       </c>
       <c r="N161" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O161">
         <v>2654</v>
@@ -12533,7 +12533,7 @@
         <v>78</v>
       </c>
       <c r="N168" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -12595,7 +12595,7 @@
         <v>1680</v>
       </c>
       <c r="N169" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O169">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         <v>1728</v>
       </c>
       <c r="N170" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -13215,7 +13215,7 @@
         <v>432</v>
       </c>
       <c r="N179" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O179">
         <v>0</v>
@@ -13277,7 +13277,7 @@
         <v>1286</v>
       </c>
       <c r="N180" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O180">
         <v>0</v>
@@ -13339,7 +13339,7 @@
         <v>1543</v>
       </c>
       <c r="N181" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O181">
         <v>0</v>
@@ -13401,7 +13401,7 @@
         <v>2143</v>
       </c>
       <c r="N182" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O182">
         <v>0</v>
@@ -13463,7 +13463,7 @@
         <v>6427</v>
       </c>
       <c r="N183" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="O183">
         <v>0</v>
